--- a/reservation_forms/024_royalty_inquiry_form--reservation_forms.xlsx
+++ b/reservation_forms/024_royalty_inquiry_form--reservation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reservation_request</t>
+          <t>reservation_request_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reservation Request</t>
+          <t>Reservation Request 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>event_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Event Time 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
